--- a/dataset/construct/dataset_splits/data_size/10_percent/merged/fold5.xlsx
+++ b/dataset/construct/dataset_splits/data_size/10_percent/merged/fold5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>495</v>
+        <v>597</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,123 +625,112 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>74.7334821722818</v>
+        <v>80.8852175070348</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>24.9680097375237</v>
       </c>
       <c r="E2" t="n">
-        <v>30.1102788964582</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>532</v>
       </c>
       <c r="I2" t="n">
-        <v>461</v>
+        <v>615</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>593</v>
       </c>
       <c r="K2" t="n">
-        <v>575</v>
+        <v>1740</v>
       </c>
       <c r="L2" t="n">
-        <v>273</v>
+        <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1072</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="P2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>0.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>28.6478227654698</v>
       </c>
       <c r="X2" t="n">
-        <v>24.35</v>
+        <v>27.9784080907002</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15530303030303</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.1914947797301</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>23.7726133940886</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>148</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1736</v>
+        <v>2169</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,91 +738,91 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>86.46788494689081</v>
+        <v>79.1083821646767</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>23.1836734693877</v>
       </c>
       <c r="E3" t="n">
-        <v>24.8579545454545</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>696.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4130</v>
+        <v>556.8</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>561.3</v>
       </c>
       <c r="K3" t="n">
-        <v>187.8</v>
+        <v>1814.5</v>
       </c>
       <c r="L3" t="n">
-        <v>186.2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>239</v>
+        <v>44.3</v>
       </c>
       <c r="N3" t="n">
-        <v>613</v>
+        <v>52.8</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>25.6557168321874</v>
       </c>
       <c r="X3" t="n">
-        <v>27.2</v>
+        <v>24.2129335077053</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.192691029900332</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.3745861981156</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.9117274486368</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -863,22 +837,13 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>368</v>
+        <v>528</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,77 +851,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.1969855755824</v>
+        <v>84.2009601490608</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>20.5498866213151</v>
       </c>
       <c r="E4" t="n">
-        <v>26.0261748958953</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>118.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>74.2</v>
+      </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>1100</v>
+        <v>275</v>
       </c>
       <c r="L4" t="n">
-        <v>297</v>
+        <v>35.2</v>
       </c>
       <c r="M4" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1657</v>
+        <v>6.5</v>
       </c>
       <c r="O4" t="n">
-        <v>33</v>
+        <v>41.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>60</v>
+        <v>13.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>22.8545963840081</v>
       </c>
       <c r="X4" t="n">
-        <v>22.35</v>
+        <v>22.0850401322991</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.226190476190476</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.9182582123759</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>22.3940969210825</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -971,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -983,24 +950,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>124</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>754</v>
+        <v>2375</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1008,88 +966,88 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>65.49301657920751</v>
+        <v>85.331470485715</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>23.4567901234567</v>
       </c>
       <c r="E5" t="n">
-        <v>31.2100121719047</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>38.3</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>121.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1730</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>197.3</v>
       </c>
       <c r="K5" t="n">
-        <v>283</v>
+        <v>388.1</v>
       </c>
       <c r="L5" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>284</v>
+        <v>5.4</v>
       </c>
       <c r="N5" t="n">
-        <v>776</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>27</v>
+        <v>14.6</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>44</v>
+        <v>24.25</v>
       </c>
       <c r="V5" t="n">
-        <v>44</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>24.7326203208556</v>
       </c>
       <c r="X5" t="n">
-        <v>23.4</v>
+        <v>24.3805715703063</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.279411764705882</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.2365673542144</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.8163986665956</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1098,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1107,24 +1065,13 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN5" t="n">
         <v>142</v>
       </c>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2006</v>
+        <v>2319</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1132,85 +1079,85 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.10314342662311</v>
+        <v>77.2493207024615</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>28.515625</v>
       </c>
       <c r="E6" t="n">
-        <v>33.8123415046491</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>55.8</v>
       </c>
       <c r="I6" t="n">
-        <v>391</v>
+        <v>46.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>14.9</v>
       </c>
       <c r="K6" t="n">
-        <v>718.6</v>
+        <v>117.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1023.4</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>535.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2277.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>140.7</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>59.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>252.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>100.6</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>22.8</v>
       </c>
       <c r="V6" t="n">
-        <v>105.6</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X6" t="n">
-        <v>27.2</v>
+        <v>22.1741916431478</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0912280701754387</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>27.6610644257703</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>27.3480481672903</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1219,36 +1166,27 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>226</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1256,88 +1194,88 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82.4873716632443</v>
+        <v>86.8191345349456</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>25.6055363321799</v>
       </c>
       <c r="E7" t="n">
-        <v>24.4897959183673</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>420</v>
       </c>
       <c r="I7" t="n">
-        <v>18300</v>
+        <v>285</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>308</v>
       </c>
       <c r="K7" t="n">
-        <v>694</v>
+        <v>1013</v>
       </c>
       <c r="L7" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2609</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X7" t="n">
-        <v>25.3</v>
+        <v>23.4220054480732</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.255172413793103</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>26.4196587726</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>25.6028939368547</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1346,31 +1284,24 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>53231569</v>
+        <v>55878046</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1378,73 +1309,71 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>79.4223134839151</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>81.1772758384668</v>
+      </c>
+      <c r="D8" t="n">
+        <v>23.7228106518761</v>
+      </c>
       <c r="E8" t="n">
-        <v>23.8754325259516</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35</v>
+      </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>680</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>200</v>
+        <v>308.08078</v>
       </c>
       <c r="M8" t="n">
-        <v>158</v>
+        <v>382.5472</v>
       </c>
       <c r="N8" t="n">
-        <v>1039</v>
+        <v>555.0932</v>
       </c>
       <c r="O8" t="n">
-        <v>464</v>
+        <v>1245.72118</v>
       </c>
       <c r="P8" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>23.929016</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>24.0359996747878</v>
       </c>
       <c r="X8" t="n">
-        <v>31.8</v>
+        <v>23.27509597989943</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>102.3</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>802.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1471,24 +1400,15 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>202</v>
-      </c>
-      <c r="AN8" t="n">
         <v>154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>53508246</v>
+        <v>52019817</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1496,117 +1416,114 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>89.3032169746749</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>86.031485284052</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25.8264462809917</v>
+      </c>
       <c r="E9" t="n">
-        <v>30.859375</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>60</v>
+      </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>119</v>
+      </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="K9" t="n">
-        <v>397</v>
+        <v>295</v>
       </c>
       <c r="L9" t="n">
-        <v>334</v>
+        <v>59</v>
       </c>
       <c r="M9" t="n">
-        <v>158</v>
+        <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>889</v>
+        <v>103</v>
       </c>
       <c r="O9" t="n">
-        <v>397</v>
+        <v>206</v>
       </c>
       <c r="P9" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>793</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>37</v>
+        <v>32.7</v>
       </c>
       <c r="V9" t="n">
-        <v>88</v>
+        <v>0.13</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>32.72225629969368</v>
       </c>
       <c r="X9" t="n">
-        <v>25.2</v>
+        <v>32.15385684991696</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.22</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>79.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>486</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>243</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>54798778</v>
+        <v>52101126</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1614,74 +1531,88 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84.1998631074606</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>78.24503764544831</v>
+      </c>
+      <c r="D10" t="n">
+        <v>34.3970401202451</v>
+      </c>
       <c r="E10" t="n">
-        <v>20.4444444444444</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>55</v>
+      </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>55</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="I10" t="n">
+        <v>92</v>
+      </c>
       <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="K10" t="n">
+        <v>301</v>
+      </c>
+      <c r="L10" t="n">
+        <v>78</v>
+      </c>
+      <c r="M10" t="n">
+        <v>92</v>
+      </c>
+      <c r="N10" t="n">
+        <v>131</v>
+      </c>
       <c r="O10" t="n">
-        <v>80</v>
+        <v>301</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="S10" t="n">
-        <v>41</v>
+        <v>232</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="V10" t="n">
-        <v>41</v>
+        <v>0.18</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>25.0828190312827</v>
       </c>
       <c r="X10" t="n">
-        <v>20.7</v>
+        <v>24.47568601281472</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>321.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1690,33 +1621,20 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>182</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>93</v>
-      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>52141139</v>
+        <v>51401967</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1724,109 +1642,110 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>91.1184120465435</v>
+        <v>66.44216290212179</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>46.7128027681661</v>
       </c>
       <c r="E11" t="n">
-        <v>25.0761930481077</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>380</v>
+      </c>
+      <c r="I11" t="n">
+        <v>577</v>
+      </c>
       <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+        <v>527</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1484</v>
+      </c>
+      <c r="L11" t="n">
+        <v>404</v>
+      </c>
+      <c r="M11" t="n">
+        <v>611</v>
+      </c>
+      <c r="N11" t="n">
+        <v>552</v>
+      </c>
       <c r="O11" t="n">
-        <v>219.60062</v>
+        <v>1567</v>
       </c>
       <c r="P11" t="n">
-        <v>97.896545</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>288.11868</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>605.61584</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>31.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>31.76732664114231</v>
       </c>
       <c r="X11" t="n">
-        <v>21.35859</v>
+        <v>31.17677129612403</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>66.61520400000001</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>339.1957</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>51517324</v>
+        <v>53628169</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1834,121 +1753,114 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>85.9247091033539</v>
+        <v>86.7077344284736</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>23.6614386154678</v>
       </c>
       <c r="E12" t="n">
-        <v>24.1287923737194</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>68</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>577</v>
+      </c>
+      <c r="I12" t="n">
+        <v>380</v>
+      </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>276</v>
       </c>
       <c r="K12" t="n">
-        <v>615</v>
+        <v>1233</v>
       </c>
       <c r="L12" t="n">
-        <v>358</v>
+        <v>577</v>
       </c>
       <c r="M12" t="n">
-        <v>454</v>
+        <v>380</v>
       </c>
       <c r="N12" t="n">
-        <v>1427</v>
+        <v>276</v>
       </c>
       <c r="O12" t="n">
-        <v>608</v>
+        <v>1233</v>
       </c>
       <c r="P12" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1373</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>27.9794389955552</v>
       </c>
       <c r="X12" t="n">
-        <v>26.7</v>
+        <v>27.19604477744247</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>86.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>575.7</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>202</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>97</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>51208627</v>
+        <v>51664457</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1956,80 +1868,82 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80.0027378507871</v>
+        <v>86.1738535249829</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>19.687825182102</v>
       </c>
       <c r="E13" t="n">
-        <v>22.1453287197232</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>407</v>
+      </c>
+      <c r="I13" t="n">
+        <v>59</v>
+      </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="K13" t="n">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="L13" t="n">
-        <v>866</v>
+        <v>401</v>
       </c>
       <c r="M13" t="n">
-        <v>922</v>
+        <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>2459</v>
+        <v>187</v>
       </c>
       <c r="O13" t="n">
-        <v>670</v>
+        <v>609</v>
       </c>
       <c r="P13" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1974</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>29.9</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>31.54450972081365</v>
       </c>
       <c r="X13" t="n">
-        <v>30.5</v>
+        <v>29.7130324995508</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.18</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>98.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>748.6</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2044,29 +1958,24 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>55008748</v>
+        <v>54240272</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2074,74 +1983,80 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>82.8692676249144</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>61.8891170431212</v>
+      </c>
+      <c r="D14" t="n">
+        <v>31.0978907517577</v>
+      </c>
       <c r="E14" t="n">
-        <v>24.2512783053324</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>59</v>
+      </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>368</v>
+      </c>
+      <c r="M14" t="n">
+        <v>201</v>
+      </c>
+      <c r="N14" t="n">
+        <v>132</v>
+      </c>
       <c r="O14" t="n">
-        <v>432</v>
+        <v>701</v>
       </c>
       <c r="P14" t="n">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1127</v>
+        <v>19</v>
       </c>
       <c r="S14" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="T14" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>97</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
-        <v>188</v>
+        <v>0.24</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>23.68225553207403</v>
       </c>
       <c r="X14" t="n">
-        <v>25.5</v>
+        <v>22.98960058416775</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>82.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2150,33 +2065,20 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>194</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>166</v>
-      </c>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>51979217</v>
+        <v>53366811</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2184,69 +2086,79 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>73.96577686516081</v>
+        <v>76.94455852156059</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>29.7777777777778</v>
       </c>
       <c r="E15" t="n">
-        <v>22.5981404958678</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
+        <v>494</v>
+      </c>
+      <c r="I15" t="n">
         <v>61</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="K15" t="n">
+        <v>675</v>
+      </c>
+      <c r="L15" t="n">
+        <v>415</v>
+      </c>
+      <c r="M15" t="n">
+        <v>52</v>
+      </c>
+      <c r="N15" t="n">
+        <v>23</v>
+      </c>
       <c r="O15" t="n">
-        <v>390.397</v>
+        <v>490</v>
       </c>
       <c r="P15" t="n">
-        <v>98.03888999999999</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>85.64113999999999</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>574.0771</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>25.4011289174665</v>
       </c>
       <c r="X15" t="n">
-        <v>25.20892</v>
+        <v>24.84228667681648</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>82.09505</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>498.84317</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2264,33 +2176,24 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>52884841</v>
+        <v>55556875</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2298,79 +2201,77 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>86.4777549623546</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>78.44763860369611</v>
+      </c>
+      <c r="D16" t="n">
+        <v>23.1481481481481</v>
+      </c>
       <c r="E16" t="n">
-        <v>28.4005479635136</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>55</v>
+      </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
-        <v>45</v>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>462</v>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>223</v>
+        <v>357.73605</v>
       </c>
       <c r="M16" t="n">
-        <v>355</v>
+        <v>230.7632</v>
       </c>
       <c r="N16" t="n">
-        <v>1041</v>
+        <v>139.53268</v>
       </c>
       <c r="O16" t="n">
-        <v>397</v>
+        <v>728.03193</v>
       </c>
       <c r="P16" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>355</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>959</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>60</v>
+        <v>24.869766</v>
       </c>
       <c r="V16" t="n">
-        <v>60</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>25.26689636522325</v>
       </c>
       <c r="X16" t="n">
-        <v>27.8</v>
+        <v>24.80530580157449</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>91.7</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>623.5</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2391,24 +2292,15 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>182</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>132</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>51798345</v>
+        <v>54760029</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2416,80 +2308,74 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>80.78850102669399</v>
+        <v>83.70157426420261</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>24.9337204898371</v>
       </c>
       <c r="E17" t="n">
-        <v>25.8264462809917</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>399</v>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>241</v>
+        <v>189</v>
       </c>
       <c r="M17" t="n">
-        <v>492</v>
+        <v>171</v>
       </c>
       <c r="N17" t="n">
-        <v>1132</v>
+        <v>98</v>
       </c>
       <c r="O17" t="n">
-        <v>399</v>
+        <v>458</v>
       </c>
       <c r="P17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>492</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1132</v>
+        <v>119</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>25.17831199713784</v>
       </c>
       <c r="X17" t="n">
-        <v>30.5</v>
+        <v>24.37403478239553</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>96.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>662.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2498,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2507,30 +2393,21 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>188</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>198</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>53585565</v>
+        <v>51368218</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2538,75 +2415,79 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>70.88569472963719</v>
+        <v>75.9972621492129</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>26.5731292517007</v>
       </c>
       <c r="E18" t="n">
-        <v>38.265306122449</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>48</v>
+      </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>222</v>
+      </c>
+      <c r="I18" t="n">
+        <v>206</v>
+      </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="K18" t="n">
-        <v>168</v>
+        <v>1026</v>
       </c>
       <c r="L18" t="n">
-        <v>48</v>
+        <v>206</v>
       </c>
       <c r="M18" t="n">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="N18" t="n">
-        <v>310</v>
+        <v>603</v>
       </c>
       <c r="O18" t="n">
-        <v>148</v>
+        <v>959</v>
       </c>
       <c r="P18" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>29.41183348338226</v>
       </c>
       <c r="X18" t="n">
-        <v>24.1</v>
+        <v>28.0169980427816</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>79.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>441.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2624,33 +2505,24 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>145</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>125</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>51756764</v>
+        <v>53036642</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2658,83 +2530,85 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>70.72416153319639</v>
+        <v>85.7741273100616</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>20.3804347826087</v>
       </c>
       <c r="E19" t="n">
-        <v>20.8209399167162</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>55</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I19" t="n">
+        <v>130</v>
+      </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K19" t="n">
-        <v>495</v>
+        <v>239</v>
       </c>
       <c r="L19" t="n">
-        <v>1030</v>
+        <v>65</v>
       </c>
       <c r="M19" t="n">
-        <v>778</v>
+        <v>130</v>
       </c>
       <c r="N19" t="n">
-        <v>2304</v>
+        <v>44</v>
       </c>
       <c r="O19" t="n">
-        <v>318</v>
+        <v>239</v>
       </c>
       <c r="P19" t="n">
-        <v>345</v>
+        <v>109</v>
       </c>
       <c r="Q19" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1017</v>
+        <v>158</v>
       </c>
       <c r="S19" t="n">
-        <v>191</v>
+        <v>267</v>
       </c>
       <c r="T19" t="n">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>16</v>
+        <v>25.1</v>
       </c>
       <c r="V19" t="n">
-        <v>346</v>
+        <v>0.29</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>25.94225572397894</v>
       </c>
       <c r="X19" t="n">
-        <v>23.4</v>
+        <v>25.04645930448084</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>73.8</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>404.5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2743,10 +2617,10 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
@@ -2755,24 +2629,15 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>164</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>168</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>51286310</v>
+        <v>53309838</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2780,82 +2645,88 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>78.258726899384</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>81.8261464750171</v>
+      </c>
+      <c r="D20" t="n">
+        <v>27.458654210327</v>
+      </c>
       <c r="E20" t="n">
-        <v>33.2179930795848</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>55</v>
+      </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>55</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>226</v>
+      </c>
+      <c r="I20" t="n">
+        <v>330</v>
+      </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="K20" t="n">
-        <v>268</v>
+        <v>673</v>
       </c>
       <c r="L20" t="n">
-        <v>374</v>
+        <v>172</v>
       </c>
       <c r="M20" t="n">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="N20" t="n">
-        <v>927</v>
+        <v>117</v>
       </c>
       <c r="O20" t="n">
-        <v>191</v>
+        <v>605</v>
       </c>
       <c r="P20" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>751</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>29.92112930127632</v>
       </c>
       <c r="X20" t="n">
-        <v>26</v>
+        <v>29.44183217898809</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>83.7</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>533.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2864,33 +2735,24 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>176</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>102</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>51588072</v>
+        <v>54948907</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2898,82 +2760,80 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>84.848733744011</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>83.53182751540039</v>
+      </c>
+      <c r="D21" t="n">
+        <v>22.1591086420524</v>
+      </c>
       <c r="E21" t="n">
-        <v>26.1224489795918</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>29</v>
+      </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>43</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>565</v>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>77</v>
+        <v>491</v>
       </c>
       <c r="M21" t="n">
-        <v>314</v>
+        <v>435</v>
       </c>
       <c r="N21" t="n">
-        <v>956</v>
+        <v>445</v>
       </c>
       <c r="O21" t="n">
-        <v>359</v>
+        <v>1371</v>
       </c>
       <c r="P21" t="n">
-        <v>63</v>
+        <v>355</v>
       </c>
       <c r="Q21" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>729</v>
+        <v>79</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>27.50197416627952</v>
       </c>
       <c r="X21" t="n">
-        <v>30.3</v>
+        <v>24.33744103661677</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>100.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>734.8</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -2991,19 +2851,10 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>123</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
